--- a/Models/Верблюды/results/Верблюды - Результаты прогнозов SARIMA средние.xlsx
+++ b/Models/Верблюды/results/Верблюды - Результаты прогнозов SARIMA средние.xlsx
@@ -463,7 +463,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>4.491418702812721e+17</v>
+        <v>2.342988110753842e+17</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.45</v>
+        <v>4.62</v>
       </c>
       <c r="C3" t="n">
-        <v>5.56</v>
+        <v>3.77</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.08</v>
+        <v>15.75</v>
       </c>
       <c r="C4" t="n">
-        <v>8.779999999999999</v>
+        <v>13.72</v>
       </c>
       <c r="D4" t="n">
-        <v>64.91</v>
+        <v>88.69</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>82.15000000000001</v>
+        <v>122.91</v>
       </c>
       <c r="C5" t="n">
-        <v>63.6</v>
+        <v>88.97</v>
       </c>
       <c r="D5" t="n">
-        <v>14.69</v>
+        <v>16.87</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.29</v>
+        <v>0.74</v>
       </c>
       <c r="C6" t="n">
-        <v>0.18</v>
+        <v>0.53</v>
       </c>
       <c r="D6" t="n">
-        <v>1.58495566170773e+21</v>
+        <v>4.481981798858405e+21</v>
       </c>
     </row>
     <row r="7">
@@ -559,7 +559,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>13.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.76</v>
+        <v>2.31</v>
       </c>
       <c r="C10" t="n">
-        <v>2.22</v>
+        <v>1.89</v>
       </c>
       <c r="D10" t="n">
-        <v>8.92</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +601,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.61</v>
+        <v>2.97</v>
       </c>
       <c r="C11" t="n">
-        <v>2.85</v>
+        <v>2.43</v>
       </c>
       <c r="D11" t="n">
-        <v>24.7</v>
+        <v>22.82</v>
       </c>
     </row>
     <row r="12">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.55</v>
+        <v>4.26</v>
       </c>
       <c r="C12" t="n">
-        <v>1.03</v>
+        <v>3.04</v>
       </c>
       <c r="D12" t="n">
-        <v>1.563890366910331e+23</v>
+        <v>3.268766828792398e+23</v>
       </c>
     </row>
     <row r="13">
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="D13" t="n">
-        <v>3.980634468878198e+19</v>
+        <v>3.587249808869536e+19</v>
       </c>
     </row>
     <row r="14">
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>71.2</v>
+        <v>200.76</v>
       </c>
       <c r="C14" t="n">
-        <v>45.58</v>
+        <v>132.3</v>
       </c>
       <c r="D14" t="n">
-        <v>225.74</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="15">
@@ -665,13 +665,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>129.23</v>
+        <v>172.36</v>
       </c>
       <c r="C15" t="n">
-        <v>89.5</v>
+        <v>129.42</v>
       </c>
       <c r="D15" t="n">
-        <v>21.15</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="16">
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.41</v>
+        <v>958.42</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9</v>
+        <v>553.86</v>
       </c>
       <c r="D16" t="n">
-        <v>4.283582583501973e+18</v>
+        <v>3.075002658089149e+21</v>
       </c>
     </row>
     <row r="17">
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>35.43</v>
+        <v>21668.28</v>
       </c>
       <c r="C17" t="n">
-        <v>23.4</v>
+        <v>12511.37</v>
       </c>
       <c r="D17" t="n">
-        <v>1.848497784684796e+21</v>
+        <v>3.031759413706881e+17</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.00953810947756e+17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.12</v>
+        <v>0.02</v>
       </c>
       <c r="C19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="D19" t="n">
-        <v>3.105163200541414e+18</v>
+        <v>4.87848243235304e+18</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>9.555317582725239e+18</v>
+        <v>3.116639736815847e+18</v>
       </c>
     </row>
     <row r="21">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>44.84</v>
+        <v>90.66</v>
       </c>
       <c r="C21" t="n">
-        <v>34.36</v>
+        <v>62.72</v>
       </c>
       <c r="D21" t="n">
-        <v>17.7</v>
+        <v>23.49</v>
       </c>
     </row>
   </sheetData>
